--- a/Data/Regression Evidence 2025/testDataNetherland1.xlsx
+++ b/Data/Regression Evidence 2025/testDataNetherland1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35593B9F-8C9F-4E90-9569-F7F4E936D8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E0E685-5145-40D0-A010-47B93CDD6768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,9 +222,6 @@
     <t>NameOnAccount</t>
   </si>
   <si>
-    <t>10700250</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
@@ -234,13 +231,13 @@
     <t>Mevr</t>
   </si>
   <si>
-    <t>Emie</t>
+    <t>Winnifred</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Bogisich</t>
+    <t>Fadel-Schoen</t>
   </si>
   <si>
     <t>071 025 8087</t>
@@ -333,9 +330,6 @@
     <t>Male</t>
   </si>
   <si>
-    <t>06/10/1997</t>
-  </si>
-  <si>
     <t>Citizen (Netherlands)</t>
   </si>
   <si>
@@ -357,16 +351,13 @@
     <t>NL 4-Weekly</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>701 Store Management (Vulam Syhohu (8701689))</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Mueller</t>
+    <t>Arlene</t>
+  </si>
+  <si>
+    <t>Christiansen</t>
   </si>
   <si>
     <t>Full-time( FT. )</t>
@@ -375,7 +366,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 49569171</t>
+    <t>Auto 17264735</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -665,9 +656,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -741,6 +729,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1267,405 +1258,405 @@
       </c>
     </row>
     <row r="2" spans="1:66" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="40">
+        <v>10700443</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" t="s">
         <v>66</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="K2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="L2" s="17">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45846</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="18">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
-      </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" t="s">
         <v>74</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="P2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="Q2" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="R2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="R2" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="17" t="s">
+      <c r="U2" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" t="s">
+        <v>80</v>
+      </c>
+      <c r="X2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z2" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB2" s="21">
+        <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
+        <v>45846</v>
+      </c>
+      <c r="AC2" s="26">
+        <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
+        <v>45846</v>
+      </c>
+      <c r="AD2" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE2" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG2" s="29">
+        <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
+        <v>45846</v>
+      </c>
+      <c r="AH2" s="21">
+        <v>44986</v>
+      </c>
+      <c r="AI2" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ2" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK2" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL2" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO2" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP2" s="32">
+        <v>25</v>
+      </c>
+      <c r="AQ2" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AU2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="T2" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="17" t="s">
+      <c r="AX2" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY2" s="35">
+        <v>100000083</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA2" s="36">
+        <v>35709</v>
+      </c>
+      <c r="BB2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="W2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB2" s="22">
-        <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45822</v>
-      </c>
-      <c r="AC2" s="27">
-        <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45822</v>
-      </c>
-      <c r="AD2" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE2" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF2" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG2" s="30">
-        <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45822</v>
-      </c>
-      <c r="AH2" s="22">
-        <v>44986</v>
-      </c>
-      <c r="AI2" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ2" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK2" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL2" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM2" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN2" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP2" s="33">
-        <v>25</v>
-      </c>
-      <c r="AQ2" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS2" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT2" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="AU2" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW2" s="19" t="s">
+      <c r="BC2" t="s">
         <v>74</v>
       </c>
-      <c r="AX2" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="AY2" s="36">
-        <v>100000059</v>
-      </c>
-      <c r="AZ2" t="s">
+      <c r="BD2" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="BF2" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="37" t="s">
+      <c r="BG2" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="BB2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF2" t="s">
+      <c r="BH2" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" s="19" t="s">
+      <c r="BI2" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" s="35" t="s">
+      <c r="BJ2" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="35" t="s">
+      <c r="BK2" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" s="35" t="s">
+      <c r="BL2" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="BL2" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BN2" s="38" t="s">
-        <v>69</v>
+      <c r="BM2">
+        <v>38</v>
+      </c>
+      <c r="BN2" s="37" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="13">
-        <v>10700252</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="40">
+        <v>10700444</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>45846</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="R3" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="T3" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="U3" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" t="s">
+        <v>80</v>
+      </c>
+      <c r="X3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y3" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z3" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="AA3" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB3" s="21">
+        <f t="shared" ca="1" si="1"/>
+        <v>45846</v>
+      </c>
+      <c r="AC3" s="26">
+        <f t="shared" ca="1" si="2"/>
+        <v>45846</v>
+      </c>
+      <c r="AD3" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE3" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF3" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG3" s="29">
+        <f t="shared" ca="1" si="3"/>
+        <v>45846</v>
+      </c>
+      <c r="AH3" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI3" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="15" t="s">
+      <c r="AJ3" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="17" t="s">
+      <c r="AK3" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL3" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM3" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO3" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP3" s="32">
+        <v>40</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS3" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AU3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="AV3" s="35">
+        <v>251</v>
+      </c>
+      <c r="AW3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
-      </c>
-      <c r="M3" s="19" t="s">
+      <c r="AX3" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY3" s="35">
+        <v>100000084</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BA3" s="36">
+        <v>35591</v>
+      </c>
+      <c r="BB3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC3" t="s">
         <v>74</v>
       </c>
-      <c r="N3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="P3" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q3" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="R3" t="s">
-        <v>75</v>
-      </c>
-      <c r="S3" s="17" t="s">
+      <c r="BD3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BE3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="T3" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA3" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
-      </c>
-      <c r="AC3" s="27">
-        <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
-      </c>
-      <c r="AD3" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF3" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG3" s="30">
-        <f t="shared" ca="1" si="3"/>
-        <v>45822</v>
-      </c>
-      <c r="AH3" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI3" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ3" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK3" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL3" s="32" t="s">
+      <c r="BF3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BG3" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH3" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI3" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="BJ3" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK3" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL3" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="AM3" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN3" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="AO3" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP3" s="33">
+      <c r="BM3">
         <v>40</v>
       </c>
-      <c r="AQ3" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AS3" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT3" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="AU3" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV3" s="36">
-        <v>251</v>
-      </c>
-      <c r="AW3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AX3" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="AY3" s="36">
-        <v>100000060</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA3" s="37">
-        <v>35591</v>
-      </c>
-      <c r="BB3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BG3" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="BH3" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="BI3" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="BJ3" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="BK3" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="BL3" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>109</v>
-      </c>
-      <c r="BN3" s="40" t="s">
-        <v>69</v>
+      <c r="BN3" s="39" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
